--- a/docentes/Rodríguez Román Leticia - Estadisticos 20231.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20231.xlsx
@@ -560,7 +560,7 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -569,10 +569,10 @@
         <v>10</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>74.36</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H3">
         <v>5.7</v>
@@ -606,19 +606,19 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F5">
         <v>19</v>
       </c>
       <c r="G5">
-        <v>47.5</v>
+        <v>48.72</v>
       </c>
       <c r="H5">
         <v>5.5</v>
@@ -632,10 +632,10 @@
         <v>13</v>
       </c>
       <c r="C6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -644,7 +644,7 @@
         <v>14</v>
       </c>
       <c r="G6">
-        <v>77.78</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H6">
         <v>6.4</v>
@@ -720,13 +720,13 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -763,13 +763,13 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D5">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E5">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -786,10 +786,10 @@
         <v>13</v>
       </c>
       <c r="C6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E6">
         <v>18</v>
@@ -874,7 +874,7 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -883,10 +883,10 @@
         <v>10</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>74.36</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H3">
         <v>5.7</v>
@@ -920,19 +920,19 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F5">
         <v>19</v>
       </c>
       <c r="G5">
-        <v>47.5</v>
+        <v>48.72</v>
       </c>
       <c r="H5">
         <v>5.5</v>
@@ -946,10 +946,10 @@
         <v>13</v>
       </c>
       <c r="C6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -958,7 +958,7 @@
         <v>14</v>
       </c>
       <c r="G6">
-        <v>77.78</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H6">
         <v>6.4</v>

--- a/docentes/Rodríguez Román Leticia - Estadisticos 20231.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="50">
   <si>
     <t>Mat</t>
   </si>
@@ -79,13 +79,25 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>ALFONSO</t>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
   </si>
   <si>
     <t>BARRAGAN</t>
@@ -94,19 +106,22 @@
     <t>CRUZ</t>
   </si>
   <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
     <t>MENDEZ</t>
   </si>
   <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>BERMUDEZ</t>
+  </si>
+  <si>
     <t>CIRUELO</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
+    <t>SANTIAGO</t>
   </si>
   <si>
     <t>MACUIXTLE</t>
@@ -115,16 +130,31 @@
     <t>CASTILLO</t>
   </si>
   <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
     <t>MONDRAGON</t>
   </si>
   <si>
+    <t>ALEX URIEL</t>
+  </si>
+  <si>
+    <t>YAMILETH</t>
+  </si>
+  <si>
     <t>GISELA GUADALUPE</t>
   </si>
   <si>
     <t>VANESSA</t>
   </si>
   <si>
-    <t>ROSA ICELA</t>
+    <t>ANGEL ABRAHAM</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>DIEGO GREGORIO</t>
   </si>
   <si>
     <t>MARIA FERNANDA</t>
@@ -133,7 +163,7 @@
     <t>RAMSES</t>
   </si>
   <si>
-    <t>DIEGO GREGORIO</t>
+    <t>JAIRO</t>
   </si>
   <si>
     <t>ANGEL ADRIAN</t>
@@ -560,7 +590,7 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -569,10 +599,10 @@
         <v>10</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>73.68000000000001</v>
+        <v>74.36</v>
       </c>
       <c r="H3">
         <v>5.7</v>
@@ -720,13 +750,13 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -874,7 +904,7 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -883,10 +913,10 @@
         <v>10</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>73.68000000000001</v>
+        <v>74.36</v>
       </c>
       <c r="H3">
         <v>5.7</v>
@@ -971,7 +1001,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1003,22 +1033,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920328</v>
+        <v>23330051920212</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1026,16 +1056,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920357</v>
+        <v>23330051920226</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1049,22 +1079,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920217</v>
+        <v>23330051920328</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1072,22 +1102,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920220</v>
+        <v>23330051920357</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1095,22 +1125,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920221</v>
+        <v>23330051920280</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1118,16 +1148,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920251</v>
+        <v>23330051920229</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1141,16 +1171,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920253</v>
+        <v>23330051920251</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1160,6 +1190,98 @@
       </c>
       <c r="G8">
         <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>23330051920220</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>23330051920221</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>23330051920230</v>
+      </c>
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>23330051920253</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Rodríguez Román Leticia - Estadisticos 20231.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="59">
   <si>
     <t>Mat</t>
   </si>
@@ -79,6 +79,9 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>VERA</t>
   </si>
   <si>
@@ -88,27 +91,36 @@
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>CUAPIO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
   </si>
   <si>
     <t>ZACARIAS</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
     <t>CRUZ</t>
   </si>
   <si>
+    <t>GILES</t>
+  </si>
+  <si>
     <t>MENDEZ</t>
   </si>
   <si>
+    <t>AUTRAN</t>
+  </si>
+  <si>
     <t>VILLA</t>
   </si>
   <si>
@@ -118,24 +130,33 @@
     <t>CIRUELO</t>
   </si>
   <si>
+    <t>MACUIXTLE</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>MACUIXTLE</t>
-  </si>
-  <si>
     <t>CASTILLO</t>
   </si>
   <si>
     <t>SANTOS</t>
   </si>
   <si>
+    <t>FIGUEROA</t>
+  </si>
+  <si>
     <t>MONDRAGON</t>
   </si>
   <si>
+    <t>AXEL AARON</t>
+  </si>
+  <si>
     <t>ALEX URIEL</t>
   </si>
   <si>
@@ -145,25 +166,31 @@
     <t>GISELA GUADALUPE</t>
   </si>
   <si>
-    <t>VANESSA</t>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>JESSICA</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>DIEGO GREGORIO</t>
+  </si>
+  <si>
+    <t>INGRID ISABEL</t>
   </si>
   <si>
     <t>ANGEL ABRAHAM</t>
   </si>
   <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>DIEGO GREGORIO</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
     <t>RAMSES</t>
   </si>
   <si>
     <t>JAIRO</t>
+  </si>
+  <si>
+    <t>ALEXA YAMILET</t>
   </si>
   <si>
     <t>ANGEL ADRIAN</t>
@@ -665,10 +692,10 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6">
         <v>14</v>
@@ -730,16 +757,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>47.22</v>
+      </c>
+      <c r="H2">
+        <v>6.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -753,16 +783,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>51.28</v>
+      </c>
+      <c r="H3">
+        <v>5.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -796,16 +829,19 @@
         <v>39</v>
       </c>
       <c r="D5">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>33.33</v>
+      </c>
+      <c r="H5">
+        <v>5.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -819,16 +855,19 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>47.37</v>
+      </c>
+      <c r="H6">
+        <v>6.4</v>
       </c>
     </row>
   </sheetData>
@@ -884,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G2">
-        <v>61.11</v>
+        <v>47.22</v>
       </c>
       <c r="H2">
-        <v>6.1</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -910,16 +949,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G3">
-        <v>74.36</v>
+        <v>51.28</v>
       </c>
       <c r="H3">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -956,16 +995,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F5">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>48.72</v>
+        <v>33.33</v>
       </c>
       <c r="H5">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -979,19 +1018,19 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>73.68000000000001</v>
+        <v>47.37</v>
       </c>
       <c r="H6">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
     </row>
   </sheetData>
@@ -1001,7 +1040,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1033,16 +1072,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920212</v>
+        <v>23330051920190</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1056,22 +1095,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920226</v>
+        <v>23330051920212</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1079,16 +1118,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920328</v>
+        <v>23330051920226</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1102,16 +1141,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920357</v>
+        <v>23330051920328</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1125,22 +1164,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920280</v>
+        <v>23330051920220</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1148,16 +1187,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920229</v>
+        <v>23330051920222</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1171,16 +1210,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920251</v>
+        <v>23330051920229</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1194,16 +1233,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920220</v>
+        <v>23330051920251</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1212,27 +1251,27 @@
         <v>12</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920221</v>
+        <v>23330051920227</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1240,22 +1279,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920230</v>
+        <v>23330051920280</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1263,16 +1302,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920253</v>
+        <v>23330051920221</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1281,6 +1320,75 @@
         <v>12</v>
       </c>
       <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>23330051920230</v>
+      </c>
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>23330051920231</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>23330051920253</v>
+      </c>
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rodríguez Román Leticia - Estadisticos 20231.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="87">
   <si>
     <t>Mat</t>
   </si>
@@ -79,121 +79,205 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CHICO</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
     <t>VERA</t>
   </si>
   <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
+    <t>SAN JUAN</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
     <t>CASTRO</t>
   </si>
   <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>CUAPIO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>AUTRAN</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>MACUIXTLE</t>
+  </si>
+  <si>
+    <t>TZITZIHUA</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>BERMUDEZ</t>
+  </si>
+  <si>
+    <t>CANDELARIO</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>CUAPIO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GILES</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>AUTRAN</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>BERMUDEZ</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>MACUIXTLE</t>
+    <t>CASTILLO</t>
   </si>
   <si>
     <t>HUERTA</t>
   </si>
   <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>FIGUEROA</t>
-  </si>
-  <si>
     <t>MONDRAGON</t>
   </si>
   <si>
+    <t>FERNANDO</t>
+  </si>
+  <si>
     <t>AXEL AARON</t>
   </si>
   <si>
     <t>ALEX URIEL</t>
   </si>
   <si>
+    <t>ANGEL JESUS</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>ANGEL GABRIEL</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>MIRIAM</t>
+  </si>
+  <si>
+    <t>ALEX TADEO</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t>FERNANDA YAMILET</t>
+  </si>
+  <si>
+    <t>DIANA LAURA</t>
+  </si>
+  <si>
+    <t>KARINA MONSERRATH</t>
+  </si>
+  <si>
+    <t>YAMILET</t>
+  </si>
+  <si>
+    <t>GIANCARLO</t>
+  </si>
+  <si>
     <t>YAMILETH</t>
   </si>
   <si>
-    <t>GISELA GUADALUPE</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
+    <t>INGRID ISABEL</t>
+  </si>
+  <si>
+    <t>DANNA PAOLA</t>
+  </si>
+  <si>
+    <t>ANGEL ABRAHAM</t>
+  </si>
+  <si>
+    <t>RAMSES</t>
   </si>
   <si>
     <t>JESSICA</t>
   </si>
   <si>
+    <t>JAIRO</t>
+  </si>
+  <si>
     <t>MARIANA</t>
   </si>
   <si>
     <t>DIEGO GREGORIO</t>
   </si>
   <si>
-    <t>INGRID ISABEL</t>
-  </si>
-  <si>
-    <t>ANGEL ABRAHAM</t>
-  </si>
-  <si>
-    <t>RAMSES</t>
-  </si>
-  <si>
-    <t>JAIRO</t>
-  </si>
-  <si>
-    <t>ALEXA YAMILET</t>
-  </si>
-  <si>
     <t>ANGEL ADRIAN</t>
+  </si>
+  <si>
+    <t>MARIEL</t>
   </si>
 </sst>
 </file>
@@ -1040,7 +1124,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1072,16 +1156,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920190</v>
+        <v>23330051920183</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1095,16 +1179,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920212</v>
+        <v>23330051920190</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="D3" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1118,22 +1202,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920226</v>
+        <v>23330051920212</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1141,16 +1225,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920328</v>
+        <v>23330051920216</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1164,22 +1248,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920220</v>
+        <v>23330051920357</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1187,22 +1271,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920222</v>
+        <v>23330051920277</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1210,16 +1294,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920229</v>
+        <v>23330051920220</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1233,16 +1317,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920251</v>
+        <v>23330051920233</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1256,62 +1340,62 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920227</v>
+        <v>23330051920234</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920280</v>
+        <v>23330051920236</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920221</v>
+        <v>23330051920271</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="D12" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1320,21 +1404,21 @@
         <v>12</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920230</v>
+        <v>23330051920335</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1343,21 +1427,21 @@
         <v>12</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920231</v>
+        <v>23330051920264</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D14" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1366,29 +1450,305 @@
         <v>12</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
+        <v>23330051920342</v>
+      </c>
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>23330051920300</v>
+      </c>
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" t="s">
+        <v>75</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>23330051920226</v>
+      </c>
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" t="s">
+        <v>76</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>23330051920227</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" t="s">
+        <v>77</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>23330051920256</v>
+      </c>
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>23330051920280</v>
+      </c>
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" t="s">
+        <v>79</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>23330051920221</v>
+      </c>
+      <c r="B21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" t="s">
+        <v>56</v>
+      </c>
+      <c r="D21" t="s">
+        <v>80</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>23330051920222</v>
+      </c>
+      <c r="B22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" t="s">
+        <v>81</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>23330051920230</v>
+      </c>
+      <c r="B23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" t="s">
+        <v>82</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>23330051920229</v>
+      </c>
+      <c r="B24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>23330051920251</v>
+      </c>
+      <c r="B25" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" t="s">
+        <v>27</v>
+      </c>
+      <c r="D25" t="s">
+        <v>84</v>
+      </c>
+      <c r="E25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
         <v>23330051920253</v>
       </c>
-      <c r="B15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="B26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" t="s">
+        <v>60</v>
+      </c>
+      <c r="D26" t="s">
+        <v>85</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s">
         <v>12</v>
       </c>
-      <c r="G15">
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>23330051920286</v>
+      </c>
+      <c r="B27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" t="s">
+        <v>86</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rodríguez Román Leticia - Estadisticos 20231.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="90">
   <si>
     <t>Mat</t>
   </si>
@@ -82,10 +82,13 @@
     <t>CHICO</t>
   </si>
   <si>
+    <t>ESPINOZA</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>VERA</t>
+    <t>NARVAEZ</t>
   </si>
   <si>
     <t>CARRERA</t>
@@ -118,9 +121,6 @@
     <t>SAN JUAN</t>
   </si>
   <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
     <t>CASTRO</t>
   </si>
   <si>
@@ -148,39 +148,42 @@
     <t>ARIAS</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>RIVERA</t>
   </si>
   <si>
+    <t>NOLASCO</t>
+  </si>
+  <si>
     <t>AUTRAN</t>
   </si>
   <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>MACUIXTLE</t>
+  </si>
+  <si>
+    <t>TZITZIHUA</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>BERMUDEZ</t>
+  </si>
+  <si>
     <t>VILLA</t>
   </si>
   <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>MACUIXTLE</t>
-  </si>
-  <si>
-    <t>TZITZIHUA</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>BERMUDEZ</t>
-  </si>
-  <si>
     <t>CANDELARIO</t>
   </si>
   <si>
@@ -202,13 +205,19 @@
     <t>MONDRAGON</t>
   </si>
   <si>
+    <t>RIOS</t>
+  </si>
+  <si>
     <t>FERNANDO</t>
   </si>
   <si>
+    <t>JULIO CESAR</t>
+  </si>
+  <si>
     <t>AXEL AARON</t>
   </si>
   <si>
-    <t>ALEX URIEL</t>
+    <t>LAZARO</t>
   </si>
   <si>
     <t>ANGEL JESUS</t>
@@ -244,9 +253,6 @@
     <t>YAMILET</t>
   </si>
   <si>
-    <t>GIANCARLO</t>
-  </si>
-  <si>
     <t>YAMILETH</t>
   </si>
   <si>
@@ -278,6 +284,9 @@
   </si>
   <si>
     <t>MARIEL</t>
+  </si>
+  <si>
+    <t>NOHEMI ANGELICA</t>
   </si>
 </sst>
 </file>
@@ -1105,16 +1114,16 @@
         <v>0</v>
       </c>
       <c r="E6">
+        <v>9</v>
+      </c>
+      <c r="F6">
         <v>10</v>
       </c>
-      <c r="F6">
-        <v>9</v>
-      </c>
       <c r="G6">
-        <v>47.37</v>
+        <v>52.63</v>
       </c>
       <c r="H6">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
     </row>
   </sheetData>
@@ -1124,7 +1133,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1162,10 +1171,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1179,16 +1188,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920190</v>
+        <v>23330051920188</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1202,16 +1211,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920212</v>
+        <v>23330051920190</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1225,22 +1234,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920216</v>
+        <v>23330051920202</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1248,16 +1257,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920357</v>
+        <v>23330051920216</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1271,16 +1280,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920277</v>
+        <v>23330051920357</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1294,7 +1303,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920220</v>
+        <v>23330051920277</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
@@ -1303,13 +1312,13 @@
         <v>47</v>
       </c>
       <c r="D8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1317,7 +1326,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920233</v>
+        <v>23330051920220</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
@@ -1326,7 +1335,7 @@
         <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1340,16 +1349,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920234</v>
+        <v>23330051920233</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1363,16 +1372,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920236</v>
+        <v>23330051920234</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1386,16 +1395,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920271</v>
+        <v>23330051920236</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="D12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1409,16 +1418,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920335</v>
+        <v>23330051920271</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1432,7 +1441,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920264</v>
+        <v>23330051920335</v>
       </c>
       <c r="B14" t="s">
         <v>32</v>
@@ -1441,7 +1450,7 @@
         <v>51</v>
       </c>
       <c r="D14" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1455,22 +1464,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920342</v>
+        <v>23330051920264</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="D15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -1478,16 +1487,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920300</v>
+        <v>23330051920342</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="D16" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1510,7 +1519,7 @@
         <v>53</v>
       </c>
       <c r="D17" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1530,10 +1539,10 @@
         <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D18" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1550,13 +1559,13 @@
         <v>23330051920256</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D19" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1576,10 +1585,10 @@
         <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D20" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1599,10 +1608,10 @@
         <v>37</v>
       </c>
       <c r="C21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D21" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1622,10 +1631,10 @@
         <v>38</v>
       </c>
       <c r="C22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D22" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1645,10 +1654,10 @@
         <v>39</v>
       </c>
       <c r="C23" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D23" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1668,10 +1677,10 @@
         <v>39</v>
       </c>
       <c r="C24" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D24" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -1691,10 +1700,10 @@
         <v>40</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D25" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -1714,10 +1723,10 @@
         <v>41</v>
       </c>
       <c r="C26" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D26" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -1737,10 +1746,10 @@
         <v>42</v>
       </c>
       <c r="C27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D27" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -1749,6 +1758,29 @@
         <v>13</v>
       </c>
       <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>23330051920303</v>
+      </c>
+      <c r="B28" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" t="s">
+        <v>62</v>
+      </c>
+      <c r="D28" t="s">
+        <v>89</v>
+      </c>
+      <c r="E28" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rodríguez Román Leticia - Estadisticos 20231.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="73">
   <si>
     <t>Mat</t>
   </si>
@@ -106,19 +106,16 @@
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>GUERRA</t>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>SAN JUAN</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
-    <t>SAN JUAN</t>
+    <t>JIMENEZ</t>
   </si>
   <si>
     <t>CASTRO</t>
@@ -130,21 +127,9 @@
     <t>ZACARIAS</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>CUAPIO</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
     <t>ARIAS</t>
   </si>
   <si>
@@ -169,15 +154,12 @@
     <t>TZITZIHUA</t>
   </si>
   <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
     <t>AGUILAR</t>
   </si>
   <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
     <t>BERMUDEZ</t>
   </si>
   <si>
@@ -190,21 +172,9 @@
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
-    <t>MONDRAGON</t>
-  </si>
-  <si>
     <t>RIOS</t>
   </si>
   <si>
@@ -235,24 +205,18 @@
     <t>MIRIAM</t>
   </si>
   <si>
-    <t>ALEX TADEO</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
-  </si>
-  <si>
     <t>FERNANDA YAMILET</t>
   </si>
   <si>
-    <t>DIANA LAURA</t>
-  </si>
-  <si>
     <t>KARINA MONSERRATH</t>
   </si>
   <si>
     <t>YAMILET</t>
   </si>
   <si>
+    <t>SABDY</t>
+  </si>
+  <si>
     <t>YAMILETH</t>
   </si>
   <si>
@@ -265,22 +229,7 @@
     <t>ANGEL ABRAHAM</t>
   </si>
   <si>
-    <t>RAMSES</t>
-  </si>
-  <si>
-    <t>JESSICA</t>
-  </si>
-  <si>
-    <t>JAIRO</t>
-  </si>
-  <si>
     <t>MARIANA</t>
-  </si>
-  <si>
-    <t>DIEGO GREGORIO</t>
-  </si>
-  <si>
-    <t>ANGEL ADRIAN</t>
   </si>
   <si>
     <t>MARIEL</t>
@@ -1016,16 +965,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G2">
-        <v>47.22</v>
+        <v>44.44</v>
       </c>
       <c r="H2">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1088,16 +1037,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F5">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G5">
-        <v>33.33</v>
+        <v>53.85</v>
       </c>
       <c r="H5">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1133,7 +1082,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1171,10 +1120,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1194,10 +1143,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1217,10 +1166,10 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1240,10 +1189,10 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1266,7 +1215,7 @@
         <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1289,7 +1238,7 @@
         <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1309,10 +1258,10 @@
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1332,10 +1281,10 @@
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1355,10 +1304,10 @@
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1372,16 +1321,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920234</v>
+        <v>23330051920271</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1395,16 +1344,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920236</v>
+        <v>23330051920264</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1418,22 +1367,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920271</v>
+        <v>23330051920342</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1441,85 +1390,85 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920335</v>
+        <v>23330051920329</v>
       </c>
       <c r="B14" t="s">
         <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D14" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920264</v>
+        <v>23330051920226</v>
       </c>
       <c r="B15" t="s">
         <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920342</v>
+        <v>23330051920227</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920226</v>
+        <v>23330051920256</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1533,16 +1482,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920227</v>
+        <v>23330051920280</v>
       </c>
       <c r="B18" t="s">
         <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1556,22 +1505,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920256</v>
+        <v>23330051920229</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D19" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1579,22 +1528,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920280</v>
+        <v>23330051920286</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="D20" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1602,185 +1551,24 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>23330051920221</v>
+        <v>23330051920303</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C21" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D21" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>23330051920222</v>
-      </c>
-      <c r="B22" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" t="s">
-        <v>58</v>
-      </c>
-      <c r="D22" t="s">
-        <v>83</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>23330051920230</v>
-      </c>
-      <c r="B23" t="s">
-        <v>39</v>
-      </c>
-      <c r="C23" t="s">
-        <v>59</v>
-      </c>
-      <c r="D23" t="s">
-        <v>84</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>12</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>23330051920229</v>
-      </c>
-      <c r="B24" t="s">
-        <v>39</v>
-      </c>
-      <c r="C24" t="s">
-        <v>60</v>
-      </c>
-      <c r="D24" t="s">
-        <v>85</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>12</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>23330051920251</v>
-      </c>
-      <c r="B25" t="s">
-        <v>40</v>
-      </c>
-      <c r="C25" t="s">
-        <v>28</v>
-      </c>
-      <c r="D25" t="s">
-        <v>86</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>12</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>23330051920253</v>
-      </c>
-      <c r="B26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C26" t="s">
-        <v>61</v>
-      </c>
-      <c r="D26" t="s">
-        <v>87</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>12</v>
-      </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>23330051920286</v>
-      </c>
-      <c r="B27" t="s">
-        <v>42</v>
-      </c>
-      <c r="C27" t="s">
-        <v>27</v>
-      </c>
-      <c r="D27" t="s">
-        <v>88</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>13</v>
-      </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>23330051920303</v>
-      </c>
-      <c r="B28" t="s">
-        <v>43</v>
-      </c>
-      <c r="C28" t="s">
-        <v>62</v>
-      </c>
-      <c r="D28" t="s">
-        <v>89</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>13</v>
-      </c>
-      <c r="G28">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rodríguez Román Leticia - Estadisticos 20231.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="85">
   <si>
     <t>Mat</t>
   </si>
@@ -91,48 +91,63 @@
     <t>NARVAEZ</t>
   </si>
   <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
     <t>CARRERA</t>
   </si>
   <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
+    <t>ZACARIAS</t>
   </si>
   <si>
     <t>BARRAGAN</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
     <t>SAN JUAN</t>
   </si>
   <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
     <t>PEREZ</t>
   </si>
   <si>
@@ -145,36 +160,42 @@
     <t>AUTRAN</t>
   </si>
   <si>
-    <t>GOMEZ</t>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>BERMUDEZ</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
   </si>
   <si>
     <t>MACUIXTLE</t>
   </si>
   <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
     <t>TZITZIHUA</t>
   </si>
   <si>
     <t>AGUILAR</t>
   </si>
   <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>BERMUDEZ</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>CANDELARIO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
     <t>RIOS</t>
   </si>
   <si>
@@ -190,18 +211,51 @@
     <t>LAZARO</t>
   </si>
   <si>
+    <t>CLAUDIA RUBI</t>
+  </si>
+  <si>
+    <t>MIGUEL ENRIQUE</t>
+  </si>
+  <si>
+    <t>NURIA BELEN</t>
+  </si>
+  <si>
+    <t>MARYSOL</t>
+  </si>
+  <si>
+    <t>ESTEFANIA</t>
+  </si>
+  <si>
+    <t>KARINA</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>SABDY</t>
+  </si>
+  <si>
+    <t>YAMILETH</t>
+  </si>
+  <si>
     <t>ANGEL JESUS</t>
   </si>
   <si>
+    <t>VALERY MIRANDA</t>
+  </si>
+  <si>
     <t>VANESSA</t>
   </si>
   <si>
-    <t>ANGEL GABRIEL</t>
+    <t>ANGEL ABRAHAM</t>
   </si>
   <si>
     <t>MARIA FERNANDA</t>
   </si>
   <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
     <t>MIRIAM</t>
   </si>
   <si>
@@ -211,28 +265,10 @@
     <t>KARINA MONSERRATH</t>
   </si>
   <si>
+    <t>MARIEL</t>
+  </si>
+  <si>
     <t>YAMILET</t>
-  </si>
-  <si>
-    <t>SABDY</t>
-  </si>
-  <si>
-    <t>YAMILETH</t>
-  </si>
-  <si>
-    <t>INGRID ISABEL</t>
-  </si>
-  <si>
-    <t>DANNA PAOLA</t>
-  </si>
-  <si>
-    <t>ANGEL ABRAHAM</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>MARIEL</t>
   </si>
   <si>
     <t>NOHEMI ANGELICA</t>
@@ -991,13 +1027,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3">
-        <v>51.28</v>
+        <v>53.85</v>
       </c>
       <c r="H3">
         <v>5.6</v>
@@ -1082,7 +1118,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1120,10 +1156,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1143,10 +1179,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D3" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1166,10 +1202,10 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D4" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1189,10 +1225,10 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1206,16 +1242,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920216</v>
+        <v>23330051920214</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1229,16 +1265,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920357</v>
+        <v>23330051920254</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1252,16 +1288,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920277</v>
+        <v>23330051920239</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1275,16 +1311,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920220</v>
+        <v>23330051920241</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1298,16 +1334,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920233</v>
+        <v>23330051920245</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1321,16 +1357,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920271</v>
+        <v>23330051920267</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="D11" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1344,22 +1380,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920264</v>
+        <v>23330051920319</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1367,45 +1403,45 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920342</v>
+        <v>23330051920329</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920329</v>
+        <v>23330051920226</v>
       </c>
       <c r="B14" t="s">
         <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D14" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1413,16 +1449,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920226</v>
+        <v>23330051920216</v>
       </c>
       <c r="B15" t="s">
         <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="D15" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1436,16 +1472,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920227</v>
+        <v>23330051920242</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D16" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1459,16 +1495,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920256</v>
+        <v>23330051920357</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="D17" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1485,13 +1521,13 @@
         <v>23330051920280</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="D18" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1505,16 +1541,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920229</v>
+        <v>23330051920220</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D19" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1528,22 +1564,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920286</v>
+        <v>23330051920229</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="D20" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1551,24 +1587,139 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
+        <v>23330051920233</v>
+      </c>
+      <c r="B21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" t="s">
+        <v>79</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>23330051920271</v>
+      </c>
+      <c r="B22" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22" t="s">
+        <v>80</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>23330051920264</v>
+      </c>
+      <c r="B23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" t="s">
+        <v>81</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>23330051920286</v>
+      </c>
+      <c r="B24" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D24" t="s">
+        <v>82</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>23330051920342</v>
+      </c>
+      <c r="B25" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" t="s">
+        <v>42</v>
+      </c>
+      <c r="D25" t="s">
+        <v>83</v>
+      </c>
+      <c r="E25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
         <v>23330051920303</v>
       </c>
-      <c r="B21" t="s">
-        <v>38</v>
-      </c>
-      <c r="C21" t="s">
-        <v>52</v>
-      </c>
-      <c r="D21" t="s">
-        <v>72</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
+      <c r="B26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" t="s">
+        <v>59</v>
+      </c>
+      <c r="D26" t="s">
+        <v>84</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s">
         <v>13</v>
       </c>
-      <c r="G21">
+      <c r="G26">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rodríguez Román Leticia - Estadisticos 20231.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="123">
   <si>
     <t>Mat</t>
   </si>
@@ -91,97 +91,163 @@
     <t>NARVAEZ</t>
   </si>
   <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CALVA</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>FUENTES</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>ALCANTARA</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>ENRIQUEZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MEJIA</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>SAN JUAN</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>NOLASCO</t>
+  </si>
+  <si>
+    <t>AUTRAN</t>
+  </si>
+  <si>
+    <t>BERMUDEZ</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>DAMIAN</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>GUZMAN</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>FERRER</t>
+  </si>
+  <si>
+    <t>SOSA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>CANDELARIO</t>
+  </si>
+  <si>
     <t>ALVAREZ</t>
   </si>
   <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>SAN JUAN</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>NOLASCO</t>
-  </si>
-  <si>
-    <t>AUTRAN</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>BERMUDEZ</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>MONTERROSAS</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
   </si>
   <si>
     <t>MACUIXTLE</t>
@@ -211,13 +277,25 @@
     <t>LAZARO</t>
   </si>
   <si>
-    <t>CLAUDIA RUBI</t>
-  </si>
-  <si>
-    <t>MIGUEL ENRIQUE</t>
-  </si>
-  <si>
-    <t>NURIA BELEN</t>
+    <t>YAMILETH</t>
+  </si>
+  <si>
+    <t>LORENA</t>
+  </si>
+  <si>
+    <t>VALERY MIRANDA</t>
+  </si>
+  <si>
+    <t>VIVIANA JOSELIN</t>
+  </si>
+  <si>
+    <t>GISELA GUADALUPE</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>ANGEL ABRAHAM</t>
   </si>
   <si>
     <t>MARYSOL</t>
@@ -235,22 +313,58 @@
     <t>SABDY</t>
   </si>
   <si>
-    <t>YAMILETH</t>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
+    <t>INGRID ISABEL</t>
+  </si>
+  <si>
+    <t>VANESA</t>
   </si>
   <si>
     <t>ANGEL JESUS</t>
   </si>
   <si>
-    <t>VALERY MIRANDA</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>ANGEL ABRAHAM</t>
+    <t>LUZ YESENIA</t>
+  </si>
+  <si>
+    <t>ANDREA</t>
+  </si>
+  <si>
+    <t>SILVANA</t>
+  </si>
+  <si>
+    <t>XIMENA ISABEL</t>
+  </si>
+  <si>
+    <t>DANNA PAOLA</t>
+  </si>
+  <si>
+    <t>BRISEIDA</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>ANA KAREN</t>
+  </si>
+  <si>
+    <t>SAMANTHA BETHANY</t>
   </si>
   <si>
     <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>DORIAN</t>
+  </si>
+  <si>
+    <t>VICTORIA VIANNEY</t>
+  </si>
+  <si>
+    <t>ANEL</t>
+  </si>
+  <si>
+    <t>ANGEL GABRIEL</t>
   </si>
   <si>
     <t>MARIANA</t>
@@ -721,7 +835,7 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -730,7 +844,13 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>39</v>
+      </c>
+      <c r="G4">
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -884,7 +1004,7 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -893,7 +1013,13 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>39</v>
+      </c>
+      <c r="G4">
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1047,16 +1173,22 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>5.13</v>
+      </c>
+      <c r="H4">
+        <v>5.3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1118,7 +1250,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1156,10 +1288,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1179,10 +1311,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1202,10 +1334,10 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1225,10 +1357,10 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="D5" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1242,16 +1374,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920214</v>
+        <v>23330051920226</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="D6" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1265,19 +1397,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920254</v>
+        <v>23330051920226</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="D7" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
         <v>11</v>
@@ -1288,19 +1420,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920239</v>
+        <v>23330051920215</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D8" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
         <v>11</v>
@@ -1311,22 +1443,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920241</v>
+        <v>23330051920242</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="D9" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1334,22 +1466,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920245</v>
+        <v>23330051920242</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="D10" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1357,22 +1489,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920267</v>
+        <v>23330051920248</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="D11" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1380,22 +1512,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920319</v>
+        <v>23330051920328</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="D12" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1403,62 +1535,62 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920329</v>
+        <v>23330051920357</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="D13" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920226</v>
+        <v>23330051920357</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
         <v>11</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920216</v>
+        <v>23330051920280</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D15" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1467,90 +1599,90 @@
         <v>11</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920242</v>
+        <v>23330051920280</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="D16" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
         <v>11</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920357</v>
+        <v>23330051920241</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="D17" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920280</v>
+        <v>23330051920245</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D18" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920220</v>
+        <v>23330051920267</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C19" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="D19" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1559,50 +1691,50 @@
         <v>12</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920229</v>
+        <v>23330051920319</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C20" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="D20" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>23330051920233</v>
+        <v>23330051920329</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C21" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D21" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1610,22 +1742,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>23330051920271</v>
+        <v>23330051920213</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C22" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="D22" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="E22" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1633,22 +1765,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>23330051920264</v>
+        <v>23330051920227</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C23" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D23" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="E23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1656,22 +1788,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>23330051920286</v>
+        <v>23330051920237</v>
       </c>
       <c r="B24" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C24" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="D24" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="E24" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F24" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1679,22 +1811,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>23330051920342</v>
+        <v>23330051920216</v>
       </c>
       <c r="B25" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C25" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D25" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1702,24 +1834,530 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
+        <v>23330051920240</v>
+      </c>
+      <c r="B26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" t="s">
+        <v>70</v>
+      </c>
+      <c r="D26" t="s">
+        <v>96</v>
+      </c>
+      <c r="E26" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" t="s">
+        <v>11</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>23330051920244</v>
+      </c>
+      <c r="B27" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" t="s">
+        <v>49</v>
+      </c>
+      <c r="D27" t="s">
+        <v>102</v>
+      </c>
+      <c r="E27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" t="s">
+        <v>11</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>23330051920250</v>
+      </c>
+      <c r="B28" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" t="s">
+        <v>71</v>
+      </c>
+      <c r="D28" t="s">
+        <v>103</v>
+      </c>
+      <c r="E28" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" t="s">
+        <v>11</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>23330051920333</v>
+      </c>
+      <c r="B29" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" t="s">
+        <v>29</v>
+      </c>
+      <c r="D29" t="s">
+        <v>104</v>
+      </c>
+      <c r="E29" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>23330051920252</v>
+      </c>
+      <c r="B30" t="s">
+        <v>42</v>
+      </c>
+      <c r="C30" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" t="s">
+        <v>105</v>
+      </c>
+      <c r="E30" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" t="s">
+        <v>11</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>23330051920256</v>
+      </c>
+      <c r="B31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" t="s">
+        <v>72</v>
+      </c>
+      <c r="D31" t="s">
+        <v>106</v>
+      </c>
+      <c r="E31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" t="s">
+        <v>11</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>23330051920257</v>
+      </c>
+      <c r="B32" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32" t="s">
+        <v>73</v>
+      </c>
+      <c r="D32" t="s">
+        <v>107</v>
+      </c>
+      <c r="E32" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" t="s">
+        <v>11</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>23330051920260</v>
+      </c>
+      <c r="B33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C33" t="s">
+        <v>74</v>
+      </c>
+      <c r="D33" t="s">
+        <v>108</v>
+      </c>
+      <c r="E33" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" t="s">
+        <v>11</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>23330051920330</v>
+      </c>
+      <c r="B34" t="s">
+        <v>45</v>
+      </c>
+      <c r="C34" t="s">
+        <v>42</v>
+      </c>
+      <c r="D34" t="s">
+        <v>109</v>
+      </c>
+      <c r="E34" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" t="s">
+        <v>11</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>23330051920272</v>
+      </c>
+      <c r="B35" t="s">
+        <v>46</v>
+      </c>
+      <c r="C35" t="s">
+        <v>55</v>
+      </c>
+      <c r="D35" t="s">
+        <v>110</v>
+      </c>
+      <c r="E35" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" t="s">
+        <v>11</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>23330051920270</v>
+      </c>
+      <c r="B36" t="s">
+        <v>47</v>
+      </c>
+      <c r="C36" t="s">
+        <v>41</v>
+      </c>
+      <c r="D36" t="s">
+        <v>111</v>
+      </c>
+      <c r="E36" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" t="s">
+        <v>11</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>23330051920207</v>
+      </c>
+      <c r="B37" t="s">
+        <v>48</v>
+      </c>
+      <c r="C37" t="s">
+        <v>40</v>
+      </c>
+      <c r="D37" t="s">
+        <v>112</v>
+      </c>
+      <c r="E37" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" t="s">
+        <v>11</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>23330051920276</v>
+      </c>
+      <c r="B38" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38" t="s">
+        <v>42</v>
+      </c>
+      <c r="D38" t="s">
+        <v>113</v>
+      </c>
+      <c r="E38" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38" t="s">
+        <v>11</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>23330051920275</v>
+      </c>
+      <c r="B39" t="s">
+        <v>50</v>
+      </c>
+      <c r="C39" t="s">
+        <v>75</v>
+      </c>
+      <c r="D39" t="s">
+        <v>114</v>
+      </c>
+      <c r="E39" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" t="s">
+        <v>11</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
+        <v>23330051920277</v>
+      </c>
+      <c r="B40" t="s">
+        <v>51</v>
+      </c>
+      <c r="C40" t="s">
+        <v>76</v>
+      </c>
+      <c r="D40" t="s">
+        <v>115</v>
+      </c>
+      <c r="E40" t="s">
+        <v>9</v>
+      </c>
+      <c r="F40" t="s">
+        <v>11</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41">
+        <v>23330051920220</v>
+      </c>
+      <c r="B41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C41" t="s">
+        <v>77</v>
+      </c>
+      <c r="D41" t="s">
+        <v>111</v>
+      </c>
+      <c r="E41" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41" t="s">
+        <v>12</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42">
+        <v>23330051920229</v>
+      </c>
+      <c r="B42" t="s">
+        <v>40</v>
+      </c>
+      <c r="C42" t="s">
+        <v>78</v>
+      </c>
+      <c r="D42" t="s">
+        <v>116</v>
+      </c>
+      <c r="E42" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" t="s">
+        <v>12</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43">
+        <v>23330051920233</v>
+      </c>
+      <c r="B43" t="s">
+        <v>41</v>
+      </c>
+      <c r="C43" t="s">
+        <v>79</v>
+      </c>
+      <c r="D43" t="s">
+        <v>117</v>
+      </c>
+      <c r="E43" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" t="s">
+        <v>12</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44">
+        <v>23330051920271</v>
+      </c>
+      <c r="B44" t="s">
+        <v>53</v>
+      </c>
+      <c r="C44" t="s">
+        <v>42</v>
+      </c>
+      <c r="D44" t="s">
+        <v>118</v>
+      </c>
+      <c r="E44" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" t="s">
+        <v>12</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45">
+        <v>23330051920264</v>
+      </c>
+      <c r="B45" t="s">
+        <v>54</v>
+      </c>
+      <c r="C45" t="s">
+        <v>80</v>
+      </c>
+      <c r="D45" t="s">
+        <v>119</v>
+      </c>
+      <c r="E45" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" t="s">
+        <v>12</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46">
+        <v>23330051920286</v>
+      </c>
+      <c r="B46" t="s">
+        <v>55</v>
+      </c>
+      <c r="C46" t="s">
+        <v>52</v>
+      </c>
+      <c r="D46" t="s">
+        <v>120</v>
+      </c>
+      <c r="E46" t="s">
+        <v>8</v>
+      </c>
+      <c r="F46" t="s">
+        <v>13</v>
+      </c>
+      <c r="G46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47">
+        <v>23330051920342</v>
+      </c>
+      <c r="B47" t="s">
+        <v>42</v>
+      </c>
+      <c r="C47" t="s">
+        <v>42</v>
+      </c>
+      <c r="D47" t="s">
+        <v>121</v>
+      </c>
+      <c r="E47" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" t="s">
+        <v>13</v>
+      </c>
+      <c r="G47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48">
         <v>23330051920303</v>
       </c>
-      <c r="B26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" t="s">
-        <v>59</v>
-      </c>
-      <c r="D26" t="s">
-        <v>84</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
+      <c r="B48" t="s">
+        <v>56</v>
+      </c>
+      <c r="C48" t="s">
+        <v>81</v>
+      </c>
+      <c r="D48" t="s">
+        <v>122</v>
+      </c>
+      <c r="E48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F48" t="s">
         <v>13</v>
       </c>
-      <c r="G26">
+      <c r="G48">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rodríguez Román Leticia - Estadisticos 20231.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20231.xlsx
@@ -1136,7 +1136,7 @@
         <v>44.44</v>
       </c>
       <c r="H2">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1162,7 +1162,7 @@
         <v>53.85</v>
       </c>
       <c r="H3">
-        <v>5.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1214,7 +1214,7 @@
         <v>53.85</v>
       </c>
       <c r="H5">
-        <v>5.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1240,7 +1240,7 @@
         <v>52.63</v>
       </c>
       <c r="H6">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Rodríguez Román Leticia - Estadisticos 20231.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="125">
   <si>
     <t>Mat</t>
   </si>
@@ -91,6 +91,9 @@
     <t>NARVAEZ</t>
   </si>
   <si>
+    <t>VERA</t>
+  </si>
+  <si>
     <t>CASTRO</t>
   </si>
   <si>
@@ -199,6 +202,9 @@
     <t>AUTRAN</t>
   </si>
   <si>
+    <t>VILLA</t>
+  </si>
+  <si>
     <t>BERMUDEZ</t>
   </si>
   <si>
@@ -223,9 +229,6 @@
     <t>GUZMAN</t>
   </si>
   <si>
-    <t>VILLA</t>
-  </si>
-  <si>
     <t>FERRER</t>
   </si>
   <si>
@@ -275,6 +278,9 @@
   </si>
   <si>
     <t>LAZARO</t>
+  </si>
+  <si>
+    <t>ALEX URIEL</t>
   </si>
   <si>
     <t>YAMILETH</t>
@@ -1136,7 +1142,7 @@
         <v>44.44</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1162,7 +1168,7 @@
         <v>53.85</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1214,7 +1220,7 @@
         <v>53.85</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1240,7 +1246,7 @@
         <v>52.63</v>
       </c>
       <c r="H6">
-        <v>7.6</v>
+        <v>5.7</v>
       </c>
     </row>
   </sheetData>
@@ -1250,7 +1256,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1288,10 +1294,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1311,10 +1317,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1334,10 +1340,10 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1357,10 +1363,10 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1374,22 +1380,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920226</v>
+        <v>23330051920212</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1400,16 +1406,16 @@
         <v>23330051920226</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
         <v>11</v>
@@ -1420,16 +1426,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920215</v>
+        <v>23330051920226</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1443,19 +1449,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920242</v>
+        <v>23330051920215</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
         <v>11</v>
@@ -1469,16 +1475,16 @@
         <v>23330051920242</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
         <v>11</v>
@@ -1489,16 +1495,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920248</v>
+        <v>23330051920242</v>
       </c>
       <c r="B11" t="s">
         <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -1512,16 +1518,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920328</v>
+        <v>23330051920248</v>
       </c>
       <c r="B12" t="s">
         <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1535,19 +1541,19 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920357</v>
+        <v>23330051920328</v>
       </c>
       <c r="B13" t="s">
         <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="D13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
         <v>11</v>
@@ -1561,16 +1567,16 @@
         <v>23330051920357</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D14" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
         <v>11</v>
@@ -1581,19 +1587,19 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920280</v>
+        <v>23330051920357</v>
       </c>
       <c r="B15" t="s">
         <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
         <v>11</v>
@@ -1607,16 +1613,16 @@
         <v>23330051920280</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D16" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F16" t="s">
         <v>11</v>
@@ -1627,22 +1633,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920241</v>
+        <v>23330051920280</v>
       </c>
       <c r="B17" t="s">
         <v>31</v>
       </c>
       <c r="C17" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="D17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -1650,16 +1656,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920245</v>
+        <v>23330051920241</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="D18" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1673,16 +1679,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920267</v>
+        <v>23330051920245</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C19" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="D19" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1696,22 +1702,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920319</v>
+        <v>23330051920267</v>
       </c>
       <c r="B20" t="s">
         <v>33</v>
       </c>
       <c r="C20" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G20">
         <v>2</v>
@@ -1719,45 +1725,45 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>23330051920329</v>
+        <v>23330051920319</v>
       </c>
       <c r="B21" t="s">
         <v>34</v>
       </c>
       <c r="C21" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D21" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>23330051920213</v>
+        <v>23330051920329</v>
       </c>
       <c r="B22" t="s">
         <v>35</v>
       </c>
       <c r="C22" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D22" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E22" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1765,16 +1771,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>23330051920227</v>
+        <v>23330051920213</v>
       </c>
       <c r="B23" t="s">
         <v>36</v>
       </c>
       <c r="C23" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D23" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
@@ -1788,16 +1794,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>23330051920237</v>
+        <v>23330051920227</v>
       </c>
       <c r="B24" t="s">
         <v>37</v>
       </c>
       <c r="C24" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D24" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E24" t="s">
         <v>9</v>
@@ -1811,19 +1817,19 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>23330051920216</v>
+        <v>23330051920237</v>
       </c>
       <c r="B25" t="s">
         <v>38</v>
       </c>
       <c r="C25" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="D25" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F25" t="s">
         <v>11</v>
@@ -1834,19 +1840,19 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>23330051920240</v>
+        <v>23330051920216</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="C26" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="D26" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="E26" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F26" t="s">
         <v>11</v>
@@ -1857,16 +1863,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>23330051920244</v>
+        <v>23330051920240</v>
       </c>
       <c r="B27" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="D27" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E27" t="s">
         <v>9</v>
@@ -1880,16 +1886,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>23330051920250</v>
+        <v>23330051920244</v>
       </c>
       <c r="B28" t="s">
         <v>40</v>
       </c>
       <c r="C28" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="D28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E28" t="s">
         <v>9</v>
@@ -1903,16 +1909,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>23330051920333</v>
+        <v>23330051920250</v>
       </c>
       <c r="B29" t="s">
         <v>41</v>
       </c>
       <c r="C29" t="s">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="D29" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E29" t="s">
         <v>9</v>
@@ -1926,16 +1932,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>23330051920252</v>
+        <v>23330051920333</v>
       </c>
       <c r="B30" t="s">
         <v>42</v>
       </c>
       <c r="C30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D30" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E30" t="s">
         <v>9</v>
@@ -1949,16 +1955,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>23330051920256</v>
+        <v>23330051920252</v>
       </c>
       <c r="B31" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="C31" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="D31" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E31" t="s">
         <v>9</v>
@@ -1972,16 +1978,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>23330051920257</v>
+        <v>23330051920256</v>
       </c>
       <c r="B32" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="C32" t="s">
         <v>73</v>
       </c>
       <c r="D32" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E32" t="s">
         <v>9</v>
@@ -1995,7 +2001,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>23330051920260</v>
+        <v>23330051920257</v>
       </c>
       <c r="B33" t="s">
         <v>44</v>
@@ -2004,7 +2010,7 @@
         <v>74</v>
       </c>
       <c r="D33" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E33" t="s">
         <v>9</v>
@@ -2018,16 +2024,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>23330051920330</v>
+        <v>23330051920260</v>
       </c>
       <c r="B34" t="s">
         <v>45</v>
       </c>
       <c r="C34" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="D34" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E34" t="s">
         <v>9</v>
@@ -2041,16 +2047,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>23330051920272</v>
+        <v>23330051920330</v>
       </c>
       <c r="B35" t="s">
         <v>46</v>
       </c>
       <c r="C35" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D35" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E35" t="s">
         <v>9</v>
@@ -2064,16 +2070,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>23330051920270</v>
+        <v>23330051920272</v>
       </c>
       <c r="B36" t="s">
         <v>47</v>
       </c>
       <c r="C36" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="D36" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E36" t="s">
         <v>9</v>
@@ -2087,16 +2093,16 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>23330051920207</v>
+        <v>23330051920270</v>
       </c>
       <c r="B37" t="s">
         <v>48</v>
       </c>
       <c r="C37" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D37" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E37" t="s">
         <v>9</v>
@@ -2110,16 +2116,16 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>23330051920276</v>
+        <v>23330051920207</v>
       </c>
       <c r="B38" t="s">
         <v>49</v>
       </c>
       <c r="C38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D38" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E38" t="s">
         <v>9</v>
@@ -2133,16 +2139,16 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>23330051920275</v>
+        <v>23330051920276</v>
       </c>
       <c r="B39" t="s">
         <v>50</v>
       </c>
       <c r="C39" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D39" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E39" t="s">
         <v>9</v>
@@ -2156,7 +2162,7 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>23330051920277</v>
+        <v>23330051920275</v>
       </c>
       <c r="B40" t="s">
         <v>51</v>
@@ -2165,7 +2171,7 @@
         <v>76</v>
       </c>
       <c r="D40" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E40" t="s">
         <v>9</v>
@@ -2179,7 +2185,7 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>23330051920220</v>
+        <v>23330051920277</v>
       </c>
       <c r="B41" t="s">
         <v>52</v>
@@ -2188,13 +2194,13 @@
         <v>77</v>
       </c>
       <c r="D41" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E41" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F41" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G41">
         <v>1</v>
@@ -2202,16 +2208,16 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>23330051920229</v>
+        <v>23330051920220</v>
       </c>
       <c r="B42" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C42" t="s">
         <v>78</v>
       </c>
       <c r="D42" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
@@ -2225,7 +2231,7 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>23330051920233</v>
+        <v>23330051920229</v>
       </c>
       <c r="B43" t="s">
         <v>41</v>
@@ -2234,7 +2240,7 @@
         <v>79</v>
       </c>
       <c r="D43" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
@@ -2248,16 +2254,16 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>23330051920271</v>
+        <v>23330051920233</v>
       </c>
       <c r="B44" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="C44" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="D44" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -2271,16 +2277,16 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>23330051920264</v>
+        <v>23330051920271</v>
       </c>
       <c r="B45" t="s">
         <v>54</v>
       </c>
       <c r="C45" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="D45" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -2294,22 +2300,22 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>23330051920286</v>
+        <v>23330051920264</v>
       </c>
       <c r="B46" t="s">
         <v>55</v>
       </c>
       <c r="C46" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="D46" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
       </c>
       <c r="F46" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G46">
         <v>1</v>
@@ -2317,16 +2323,16 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>23330051920342</v>
+        <v>23330051920286</v>
       </c>
       <c r="B47" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="C47" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D47" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
@@ -2340,16 +2346,16 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>23330051920303</v>
+        <v>23330051920342</v>
       </c>
       <c r="B48" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="C48" t="s">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="D48" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -2358,6 +2364,29 @@
         <v>13</v>
       </c>
       <c r="G48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49">
+        <v>23330051920303</v>
+      </c>
+      <c r="B49" t="s">
+        <v>57</v>
+      </c>
+      <c r="C49" t="s">
+        <v>82</v>
+      </c>
+      <c r="D49" t="s">
+        <v>124</v>
+      </c>
+      <c r="E49" t="s">
+        <v>8</v>
+      </c>
+      <c r="F49" t="s">
+        <v>13</v>
+      </c>
+      <c r="G49">
         <v>1</v>
       </c>
     </row>
